--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60484CF2-DFA4-400F-BF5A-656CD7BF8855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F64A699-9C3A-4274-8CDB-F956CD9711C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -104,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pirze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>skin_res</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -390,6 +386,10 @@
   </si>
   <si>
     <t>카드의 스킬 설명 텍스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prize</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,7 +565,7 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#desc"/>
-    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="pirze"/>
+    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
     <tableColumn id="19" xr3:uid="{3E5C884A-7EF6-4486-A1A0-D6FED59BF178}" name="on_play_condition_type"/>
@@ -915,7 +915,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -983,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1016,38 +1016,38 @@
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
       <c r="F1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L1" s="9"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="R1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -1058,55 +1058,55 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
       <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>38</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>39</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
         <v>40</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>41</v>
       </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" t="s">
-        <v>52</v>
-      </c>
       <c r="R2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" t="s">
         <v>47</v>
-      </c>
-      <c r="S2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -1124,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -1139,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>5</v>
@@ -1188,22 +1188,22 @@
         <v>300</v>
       </c>
       <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
+        <v>-1</v>
+      </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="s">
         <v>28</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-      <c r="H4">
-        <v>-1</v>
-      </c>
-      <c r="I4">
-        <v>-1</v>
-      </c>
-      <c r="J4">
-        <v>-1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1253,10 +1253,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1267,22 +1267,22 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1294,10 +1294,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>6</v>
@@ -1314,16 +1314,16 @@
         <v>9999</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1359,15 +1359,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="D1" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1378,22 +1378,22 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
         <v>66</v>
-      </c>
-      <c r="G2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1405,7 +1405,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>5</v>
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -1474,34 +1474,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" t="s">
-        <v>78</v>
-      </c>
       <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
         <v>82</v>
       </c>
-      <c r="H2" t="s">
-        <v>83</v>
-      </c>
       <c r="I2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
         <v>70</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>71</v>
-      </c>
-      <c r="K2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1511,13 +1511,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -1543,16 +1543,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -1561,7 +1561,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J4">
         <v>0</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F64A699-9C3A-4274-8CDB-F956CD9711C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B84DC9-1606-4978-874C-C117CA76E68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16305" yWindow="-1905" windowWidth="16410" windowHeight="18315" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,9 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>after_arts_effect_id2</t>
-  </si>
-  <si>
     <t>before_arts_effect_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -305,14 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>use_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>use_play_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#group</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -390,6 +379,31 @@
   </si>
   <si>
     <t>prize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>after_arts_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>before_use_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>after_use_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>string(128)</t>
+  </si>
+  <si>
+    <t>pow 300 이하 적 1장 파괴(승점 x)</t>
+  </si>
+  <si>
+    <t>(효과없음)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,7 +411,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,8 +441,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,8 +500,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FF5B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -491,11 +532,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -515,6 +567,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -560,14 +617,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:S4" totalsRowShown="0">
-  <autoFilter ref="A2:S4" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T4" totalsRowShown="0">
+  <autoFilter ref="A2:T4" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
+    <tableColumn id="5" xr3:uid="{22935B4D-E8E1-46B9-9B94-D1E2C10B74EF}" name="desc"/>
     <tableColumn id="19" xr3:uid="{3E5C884A-7EF6-4486-A1A0-D6FED59BF178}" name="on_play_condition_type"/>
     <tableColumn id="20" xr3:uid="{F7DC9C28-B2FA-4A46-8C80-E1718BB22F79}" name="on_play_condition_value1"/>
     <tableColumn id="21" xr3:uid="{4E5F462A-B93A-4582-B6D7-603E6CD1D818}" name="on_play_condition_value2"/>
@@ -577,7 +635,7 @@
     <tableColumn id="33" xr3:uid="{5911D336-1F67-4FCC-9F5D-6F170FE4163D}" name="arts_condition_vaule1"/>
     <tableColumn id="34" xr3:uid="{AAFC2702-D99E-4FCA-B62E-06BEDDE4A348}" name="arts_condition_vaule2"/>
     <tableColumn id="36" xr3:uid="{1BB51C8F-A1E5-43EE-8DBB-33DD7E89CBB0}" name="before_arts_effect_id"/>
-    <tableColumn id="35" xr3:uid="{7B5B7FE9-F4FD-4F2B-B7CB-706949EAAA6A}" name="after_arts_effect_id2"/>
+    <tableColumn id="35" xr3:uid="{7B5B7FE9-F4FD-4F2B-B7CB-706949EAAA6A}" name="after_arts_effect_id"/>
     <tableColumn id="39" xr3:uid="{99DEE245-8357-4369-93DC-933C127809F3}" name="unit_passive_id1"/>
     <tableColumn id="40" xr3:uid="{6F79C352-FDFC-420F-8242-ED954F95CAA9}" name="unit_passive_id2"/>
     <tableColumn id="10" xr3:uid="{2B97404B-E8EB-4E85-9C4E-CFCF5D725C33}" name="unit_start_up_id1"/>
@@ -605,17 +663,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:H4" totalsRowShown="0" tableBorderDxfId="0">
-  <autoFilter ref="A2:H4" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:I4" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="A2:I4" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8D4780BB-DB0E-4DB7-98EE-B9656815F7E3}" name="id"/>
     <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{E1E06BC9-C21F-44D1-AEEB-BA85426B8332}" name="skill_cost"/>
+    <tableColumn id="9" xr3:uid="{485720BB-2022-433F-9895-E86C6D3C14D4}" name="desc"/>
     <tableColumn id="4" xr3:uid="{B1591891-D015-470D-84EF-F5BCE8D0B39A}" name="use_condition_type"/>
     <tableColumn id="5" xr3:uid="{679497A7-A7A1-4666-85D3-098B0B4B862D}" name="use_condition_value1"/>
     <tableColumn id="6" xr3:uid="{57B82F79-74DE-4875-BCDC-DEF43858E6A9}" name="use_condition_value2"/>
-    <tableColumn id="7" xr3:uid="{04160E34-BAA6-4F91-AE2C-A00329E42C34}" name="use_play_effect_id"/>
-    <tableColumn id="8" xr3:uid="{D224225B-4E64-4356-A1B4-49989904FB92}" name="use_effect_id"/>
+    <tableColumn id="7" xr3:uid="{04160E34-BAA6-4F91-AE2C-A00329E42C34}" name="before_use_effect_id"/>
+    <tableColumn id="8" xr3:uid="{D224225B-4E64-4356-A1B4-49989904FB92}" name="after_use_effect_id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -963,7 +1022,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -997,60 +1056,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E6BAE-6D4F-4269-A5A9-7C25ADDEB0D7}">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="25.5" customWidth="1"/>
-    <col min="18" max="18" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="11.625" customWidth="1"/>
-    <col min="23" max="23" width="13.5" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="25.5" customWidth="1"/>
+    <col min="19" max="19" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="11.625" customWidth="1"/>
+    <col min="24" max="24" width="13.5" customWidth="1"/>
+    <col min="25" max="25" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
-      <c r="F1" s="5" t="s">
+    <row r="1" spans="1:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="G1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="9"/>
       <c r="M1" s="9"/>
-      <c r="N1" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1118,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1066,50 +1126,53 @@
       <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>38</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>39</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>40</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>44</v>
       </c>
       <c r="O2" t="s">
         <v>43</v>
       </c>
       <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" t="s">
-        <v>51</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" t="s">
         <v>46</v>
       </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1123,11 +1186,11 @@
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>5</v>
@@ -1139,10 +1202,10 @@
         <v>5</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>5</v>
@@ -1165,13 +1228,16 @@
       <c r="S3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="3"/>
+      <c r="T3" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="3"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>11001</v>
       </c>
@@ -1188,10 +1254,10 @@
         <v>300</v>
       </c>
       <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1202,11 +1268,11 @@
       <c r="J4">
         <v>-1</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4" t="s">
         <v>28</v>
-      </c>
-      <c r="L4">
-        <v>-1</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1227,6 +1293,9 @@
         <v>-1</v>
       </c>
       <c r="S4">
+        <v>-1</v>
+      </c>
+      <c r="T4">
         <v>-1</v>
       </c>
     </row>
@@ -1253,10 +1322,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1267,10 +1336,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -1294,7 +1363,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>24</v>
@@ -1314,16 +1383,16 @@
         <v>9999</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1346,31 +1415,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D387B383-5476-4EAA-BAC3-1341BA705F84}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="D1" s="5" t="s">
+    <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,25 +1448,28 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>64</v>
       </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>67</v>
-      </c>
       <c r="H2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="I2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -1404,11 +1477,11 @@
       <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
@@ -1419,8 +1492,11 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>21001</v>
       </c>
@@ -1430,11 +1506,11 @@
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4">
-        <v>-1</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -1443,6 +1519,9 @@
         <v>-1</v>
       </c>
       <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
         <v>210011</v>
       </c>
     </row>
@@ -1474,34 +1553,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1511,13 +1590,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -1526,7 +1605,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -1543,16 +1622,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -1561,7 +1640,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J4">
         <v>0</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\카드 데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B84DC9-1606-4978-874C-C117CA76E68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F3DDE6-00D1-4743-B318-C430102DDE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16305" yWindow="-1905" windowWidth="16410" windowHeight="18315" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,371 +40,503 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="126">
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>슬라임</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int32</t>
   </si>
   <si>
     <t>int32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>string(64)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ECardType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>max_deck_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>byte</t>
   </si>
   <si>
     <t>byte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>파이어볼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>#desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pirze</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>skin_res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>String(128)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>asset/m1_tmp/card_img/u_slime.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>asset/m1_tmp/card_img/s_fire_ball.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>arts_cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>card_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>arts_condition_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>card_condition_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ECardCondition</t>
   </si>
   <si>
     <t>card_condition_value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>card_condition_value2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
     <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.Unit - CardUnit 테이블
 2.Skill - CardSkill 테이블</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 카드 등장 조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아츠 사용 조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 카드 등장 직전 효과
 (ex 릴리스 소재)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>on_play_condition_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>등장 이후 효과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>on_play_condition_value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>on_play_condition_value2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>before_play_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>on_play_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>arts_condition_vaule1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>arts_condition_vaule2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아츠 사용 직후 효과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>before_arts_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>아츠 사용 직전 효과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>unit_start_up_id1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>unit_start_up_id2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 기동 효과 1번 외래키</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 기동 효과 2번 외래키</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>unit_passive_id1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>unit_passive_id2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 패시브 1번 외래키
 (미구현)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>유닛 패시브 2번 외래키
 (미구현)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>use_count_per_turn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>턴당 발동 가능 횟수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>더미데이터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EnemyUnitExist</t>
   </si>
   <si>
     <t>기동 효과 사용 조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>skill_cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>스칼 카드 사용 조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>스킬 카드 사용 직전 효과
 (ex 릴리스 소재)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>사용 이후 효과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>use_condition_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>use_condition_value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>use_condition_value2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>#group</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_function_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_function_value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_function_value2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ECardEffectFunctionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_target_value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OppentUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>pow 300 이하 적 1장 파괴(승점 x)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_target_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_target_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ECardEffectTargetType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ECardEffectTargetCondition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PowerUnderOrEqual</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_target_condition_value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>effect_target_condition_value2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KillUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string(128)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카드의 스킬 설명 텍스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>before_use_effect_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>after_use_effect_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>after_arts_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>before_use_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>after_use_effect_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>string(128)</t>
-  </si>
-  <si>
-    <t>pow 300 이하 적 1장 파괴(승점 x)</t>
-  </si>
-  <si>
-    <t>(효과없음)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>String(64)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#decs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 설명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>학습</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화물약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마나물약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain_Mana</t>
+  </si>
+  <si>
+    <t>Gain_Mana</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power_Up</t>
+  </si>
+  <si>
+    <t>Power_Up</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 덱에서 카드 1장을 뽑는다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 필드 유닛 1장 pow+200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신은 이번턴 마나 2를 얻는다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnDeck</t>
+  </si>
+  <si>
+    <t>OwnUnit</t>
+  </si>
+  <si>
+    <t>OwnMana</t>
+  </si>
+  <si>
+    <t>DeckHighOrEqual</t>
+  </si>
+  <si>
+    <t>레드슬라임</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>킹슬라임</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>애벌레</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽시드래곤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭탄벌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 1장 데미지 200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damege</t>
+  </si>
+  <si>
+    <t>적 1장 파괴(승점 x)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간색 슬라임이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>킹슬라임이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장 시 상대의 유닛 1장을 지정 후 데미지 200을 준다.(적이 없으면 효과는 사용하지 않는다.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장 시 자신의 덱에서 카드 1장을 드로우한다.(덱이 0장이면 효과를 발동하지 않는다.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장 시 상대의 유닛 1장을 지정 후 파괴한다. 이 효과로 파괴한 유닛의 승점은 얻지 못한다.(적이 없으면 효과는 사용하지 않는다.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m2_tmp/card_img/Red_Slime.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m3_tmp/card_img/King_Slime.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m4_tmp/card_img/Small_Worm.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m5_tmp/card_img/Pixie_Dragon.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m6_tmp/card_img/Bomb_Bee.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m2_tmp/card_img/Learning.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m3_tmp/card_img/Strengthen_Potion.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m4_tmp/card_img/Mana_Potion.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -417,6 +549,14 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,22 +582,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C5700"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,14 +635,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FF5B9BD5"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -533,25 +671,33 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
       <right/>
       <top style="thin">
-        <color rgb="FF9BC2E6"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF9BC2E6"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -566,14 +712,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
+    <cellStyle name="보통" xfId="1" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -603,8 +750,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E5" totalsRowShown="0">
-  <autoFilter ref="A2:E5" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E9" totalsRowShown="0">
+  <autoFilter ref="A2:E9" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AA48A7AE-3BB5-4D28-B310-C246BE1D73A9}" name="id"/>
     <tableColumn id="2" xr3:uid="{736DFCAA-9BE9-4E13-AC78-9D961C82FC72}" name="name"/>
@@ -617,15 +764,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T4" totalsRowShown="0">
-  <autoFilter ref="A2:T4" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T9" totalsRowShown="0">
+  <autoFilter ref="A2:T9" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
-    <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#desc"/>
-    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
+    <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
+    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="pirze"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
-    <tableColumn id="5" xr3:uid="{22935B4D-E8E1-46B9-9B94-D1E2C10B74EF}" name="desc"/>
     <tableColumn id="19" xr3:uid="{3E5C884A-7EF6-4486-A1A0-D6FED59BF178}" name="on_play_condition_type"/>
     <tableColumn id="20" xr3:uid="{F7DC9C28-B2FA-4A46-8C80-E1718BB22F79}" name="on_play_condition_value1"/>
     <tableColumn id="21" xr3:uid="{4E5F462A-B93A-4582-B6D7-603E6CD1D818}" name="on_play_condition_value2"/>
@@ -640,19 +786,19 @@
     <tableColumn id="40" xr3:uid="{6F79C352-FDFC-420F-8242-ED954F95CAA9}" name="unit_passive_id2"/>
     <tableColumn id="10" xr3:uid="{2B97404B-E8EB-4E85-9C4E-CFCF5D725C33}" name="unit_start_up_id1"/>
     <tableColumn id="11" xr3:uid="{E924433F-E951-4720-83F2-5B27EC07B4C3}" name="unit_start_up_id2"/>
+    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#decs"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}" name="UnitStartUp" displayName="UnitStartUp" ref="A2:H4" totalsRowShown="0">
-  <autoFilter ref="A2:H4" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}" name="UnitStartUp" displayName="UnitStartUp" ref="A2:G4" totalsRowShown="0">
+  <autoFilter ref="A2:G4" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{AAEBA0B0-7565-4B13-B9C8-A4A5F0860F43}" name="id"/>
     <tableColumn id="2" xr3:uid="{97590F1E-75D6-4CE3-A145-DD2939DDB4CA}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{38287567-1E25-443D-BC28-215FFAA01862}" name="use_count_per_turn"/>
-    <tableColumn id="8" xr3:uid="{77EAFF1F-30F5-4777-92D2-FA0A03D23134}" name="desc"/>
     <tableColumn id="4" xr3:uid="{F1C6AF9B-CC4F-4176-9832-5049338F1646}" name="card_condition_type"/>
     <tableColumn id="5" xr3:uid="{ACD7DAA8-ADC5-40E6-8B16-A451214C5B84}" name="card_condition_value1"/>
     <tableColumn id="6" xr3:uid="{566E7172-0BB2-49AD-BEE7-4519B8ED7880}" name="card_condition_value2"/>
@@ -663,13 +809,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:I4" totalsRowShown="0" tableBorderDxfId="0">
-  <autoFilter ref="A2:I4" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:H7" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="A2:H7" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8D4780BB-DB0E-4DB7-98EE-B9656815F7E3}" name="id"/>
     <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{E1E06BC9-C21F-44D1-AEEB-BA85426B8332}" name="skill_cost"/>
-    <tableColumn id="9" xr3:uid="{485720BB-2022-433F-9895-E86C6D3C14D4}" name="desc"/>
     <tableColumn id="4" xr3:uid="{B1591891-D015-470D-84EF-F5BCE8D0B39A}" name="use_condition_type"/>
     <tableColumn id="5" xr3:uid="{679497A7-A7A1-4666-85D3-098B0B4B862D}" name="use_condition_value1"/>
     <tableColumn id="6" xr3:uid="{57B82F79-74DE-4875-BCDC-DEF43858E6A9}" name="use_condition_value2"/>
@@ -681,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K4" totalsRowShown="0">
-  <autoFilter ref="A2:K4" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K10" totalsRowShown="0">
+  <autoFilter ref="A2:K10" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{293ED03F-3ECA-45BE-AFB4-C19E49058BDA}" name="id"/>
     <tableColumn id="2" xr3:uid="{301FB54A-AD16-4587-A00B-B96F748C89A7}" name="#group"/>
@@ -963,18 +1108,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.25" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -991,7 +1137,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1008,7 +1154,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1022,31 +1168,167 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>21001</v>
+        <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>11003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>11006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>21001</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>21002</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="14">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>21003</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>21004</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="14">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1056,127 +1338,132 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E6BAE-6D4F-4269-A5A9-7C25ADDEB0D7}">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="25.5" customWidth="1"/>
-    <col min="19" max="19" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="11.625" customWidth="1"/>
-    <col min="24" max="24" width="13.5" customWidth="1"/>
-    <col min="25" max="25" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="25.5" customWidth="1"/>
+    <col min="18" max="18" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="110.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="11.625" customWidth="1"/>
+    <col min="23" max="23" width="13.5" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="33" x14ac:dyDescent="0.3">
-      <c r="G1" s="5" t="s">
-        <v>30</v>
-      </c>
+    <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="I1" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="J1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="L1" s="9"/>
       <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
+      <c r="N1" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="O1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" t="s">
         <v>84</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" t="s">
-        <v>43</v>
-      </c>
       <c r="P2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1186,11 +1473,11 @@
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>89</v>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>5</v>
@@ -1202,10 +1489,10 @@
         <v>5</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>5</v>
@@ -1229,15 +1516,14 @@
         <v>5</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>11001</v>
       </c>
@@ -1254,10 +1540,10 @@
         <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1268,39 +1554,349 @@
       <c r="J4">
         <v>-1</v>
       </c>
-      <c r="K4">
-        <v>-1</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4">
+        <v>-1</v>
+      </c>
+      <c r="M4">
+        <v>-1</v>
+      </c>
+      <c r="N4">
+        <v>-1</v>
+      </c>
+      <c r="O4">
+        <v>-1</v>
+      </c>
+      <c r="P4">
+        <v>-1</v>
+      </c>
+      <c r="Q4">
+        <v>-1</v>
+      </c>
+      <c r="R4">
+        <v>-1</v>
+      </c>
+      <c r="S4">
+        <v>-1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>11002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
+      </c>
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="M4">
-        <v>-1</v>
-      </c>
-      <c r="N4">
-        <v>-1</v>
-      </c>
-      <c r="O4">
-        <v>-1</v>
-      </c>
-      <c r="P4">
-        <v>-1</v>
-      </c>
-      <c r="Q4">
-        <v>-1</v>
-      </c>
-      <c r="R4">
-        <v>-1</v>
-      </c>
-      <c r="S4">
-        <v>-1</v>
-      </c>
-      <c r="T4">
-        <v>-1</v>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+      <c r="H5">
+        <v>-1</v>
+      </c>
+      <c r="I5">
+        <v>-1</v>
+      </c>
+      <c r="J5">
+        <v>-1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
+        <v>-1</v>
+      </c>
+      <c r="M5">
+        <v>-1</v>
+      </c>
+      <c r="N5">
+        <v>-1</v>
+      </c>
+      <c r="O5">
+        <v>-1</v>
+      </c>
+      <c r="P5">
+        <v>-1</v>
+      </c>
+      <c r="Q5">
+        <v>-1</v>
+      </c>
+      <c r="R5">
+        <v>-1</v>
+      </c>
+      <c r="S5">
+        <v>-1</v>
+      </c>
+      <c r="T5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>11003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>800</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+      <c r="J6">
+        <v>-1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>-1</v>
+      </c>
+      <c r="M6">
+        <v>-1</v>
+      </c>
+      <c r="N6">
+        <v>-1</v>
+      </c>
+      <c r="O6">
+        <v>-1</v>
+      </c>
+      <c r="P6">
+        <v>-1</v>
+      </c>
+      <c r="Q6">
+        <v>-1</v>
+      </c>
+      <c r="R6">
+        <v>-1</v>
+      </c>
+      <c r="S6">
+        <v>-1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7">
+        <v>-1</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
+      </c>
+      <c r="J7">
+        <v>210015</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>-1</v>
+      </c>
+      <c r="M7">
+        <v>-1</v>
+      </c>
+      <c r="N7">
+        <v>-1</v>
+      </c>
+      <c r="O7">
+        <v>-1</v>
+      </c>
+      <c r="P7">
+        <v>-1</v>
+      </c>
+      <c r="Q7">
+        <v>-1</v>
+      </c>
+      <c r="R7">
+        <v>-1</v>
+      </c>
+      <c r="S7">
+        <v>-1</v>
+      </c>
+      <c r="T7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+      <c r="H8">
+        <v>-1</v>
+      </c>
+      <c r="I8">
+        <v>-1</v>
+      </c>
+      <c r="J8">
+        <v>210016</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>-1</v>
+      </c>
+      <c r="M8">
+        <v>-1</v>
+      </c>
+      <c r="N8">
+        <v>-1</v>
+      </c>
+      <c r="O8">
+        <v>-1</v>
+      </c>
+      <c r="P8">
+        <v>-1</v>
+      </c>
+      <c r="Q8">
+        <v>-1</v>
+      </c>
+      <c r="R8">
+        <v>-1</v>
+      </c>
+      <c r="S8">
+        <v>-1</v>
+      </c>
+      <c r="T8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>11006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>300</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+      <c r="H9">
+        <v>-1</v>
+      </c>
+      <c r="I9">
+        <v>-1</v>
+      </c>
+      <c r="J9">
+        <v>210017</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9">
+        <v>-1</v>
+      </c>
+      <c r="M9">
+        <v>-1</v>
+      </c>
+      <c r="N9">
+        <v>-1</v>
+      </c>
+      <c r="O9">
+        <v>-1</v>
+      </c>
+      <c r="P9">
+        <v>-1</v>
+      </c>
+      <c r="Q9">
+        <v>-1</v>
+      </c>
+      <c r="R9">
+        <v>-1</v>
+      </c>
+      <c r="S9">
+        <v>-1</v>
+      </c>
+      <c r="T9" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1310,25 +1906,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64D7676-E8C5-4ED3-9B18-1BAFD4D2AEAC}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.625" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1336,25 +1932,22 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1363,49 +1956,43 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>9999</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
         <v>9999</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1415,32 +2002,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D387B383-5476-4EAA-BAC3-1341BA705F84}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" customWidth="1"/>
-    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="E1" s="5" t="s">
-        <v>59</v>
-      </c>
+    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="D1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="5"/>
       <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="G1" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="H1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1448,28 +2034,25 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>88</v>
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -1477,11 +2060,11 @@
       <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>89</v>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
@@ -1492,11 +2075,8 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>21001</v>
       </c>
@@ -1506,27 +2086,102 @@
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>-1</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+      <c r="H4">
+        <v>210011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>21002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5">
+        <v>-1</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+      <c r="H5">
+        <v>210012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>21003</v>
+      </c>
+      <c r="B6" t="s">
         <v>90</v>
       </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>-1</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-      <c r="H4">
-        <v>-1</v>
-      </c>
-      <c r="I4">
-        <v>210011</v>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6">
+        <v>-1</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+      <c r="H6">
+        <v>210013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>21004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7">
+        <v>-1</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7">
+        <v>210014</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1536,11 +2191,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9DDD54-1F13-4B9B-9D90-4E3358700141}">
-  <dimension ref="A2:K4"/>
+  <dimension ref="A2:K10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
-    <col min="3" max="3" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="19.375" customWidth="1"/>
     <col min="6" max="6" width="26.75" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="29.5" customWidth="1"/>
@@ -1553,34 +2208,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1590,13 +2245,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -1605,7 +2260,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -1622,16 +2277,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
         <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -1640,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1649,8 +2304,218 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>210012</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>-1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>210013</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>210014</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7">
+        <v>-1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>210015</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>210016</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+      <c r="H9">
+        <v>-1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>210017</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\카드 데이터\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F3DDE6-00D1-4743-B318-C430102DDE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624588DC-5C54-439F-AA0C-52B983F5AD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -116,14 +116,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>asset/m1_tmp/card_img/u_slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m1_tmp/card_img/s_fire_ball.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>arts_cost</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -472,13 +464,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>적 1장 데미지 200</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damege</t>
-  </si>
-  <si>
     <t>적 1장 파괴(승점 x)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -507,35 +492,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>asset/m2_tmp/card_img/Red_Slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m3_tmp/card_img/King_Slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m4_tmp/card_img/Small_Worm.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m5_tmp/card_img/Pixie_Dragon.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m6_tmp/card_img/Bomb_Bee.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m2_tmp/card_img/Learning.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m3_tmp/card_img/Strengthen_Potion.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>asset/m4_tmp/card_img/Mana_Potion.png</t>
+    <t>DamegeToUnit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 1장 데미지 200(승점X)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/u_slime.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Red_Slime.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/King_Slime.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Small_Worm.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Pixie_Dragon.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Bomb_Bee.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/s_fire_ball.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Learning.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Strengthen_Potion.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/Mana_Potion.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +652,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -683,6 +684,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -693,7 +714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -717,6 +738,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
@@ -750,8 +775,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E9" totalsRowShown="0">
-  <autoFilter ref="A2:E9" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E13" totalsRowShown="0">
+  <autoFilter ref="A2:E13" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AA48A7AE-3BB5-4D28-B310-C246BE1D73A9}" name="id"/>
     <tableColumn id="2" xr3:uid="{736DFCAA-9BE9-4E13-AC78-9D961C82FC72}" name="name"/>
@@ -769,6 +794,7 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
+    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#decs"/>
     <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="pirze"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
@@ -786,7 +812,6 @@
     <tableColumn id="40" xr3:uid="{6F79C352-FDFC-420F-8242-ED954F95CAA9}" name="unit_passive_id2"/>
     <tableColumn id="10" xr3:uid="{2B97404B-E8EB-4E85-9C4E-CFCF5D725C33}" name="unit_start_up_id1"/>
     <tableColumn id="11" xr3:uid="{E924433F-E951-4720-83F2-5B27EC07B4C3}" name="unit_start_up_id2"/>
-    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#decs"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1120,7 +1145,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1171,7 +1196,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1179,7 +1204,7 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -1188,7 +1213,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,7 +1221,7 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1205,7 +1230,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1213,7 +1238,7 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -1222,7 +1247,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1230,7 +1255,7 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -1239,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1247,7 +1272,7 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -1256,7 +1281,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1273,7 +1298,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1281,7 +1306,7 @@
         <v>21002</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>14</v>
@@ -1298,7 +1323,7 @@
         <v>21003</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -1311,19 +1336,19 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
+      <c r="A13" s="15">
         <v>21004</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="17">
         <v>2</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="18" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1342,57 +1367,57 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="25.5" customWidth="1"/>
-    <col min="18" max="18" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="110.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="11.625" customWidth="1"/>
-    <col min="23" max="23" width="13.5" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="110.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="25.5" customWidth="1"/>
+    <col min="19" max="19" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="11.625" customWidth="1"/>
+    <col min="24" max="24" width="13.5" customWidth="1"/>
+    <col min="25" max="25" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="9"/>
+      <c r="K1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="M1" s="9"/>
-      <c r="N1" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="7" t="s">
-        <v>52</v>
+      <c r="P1" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>87</v>
+        <v>46</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -1400,61 +1425,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>40</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>42</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" t="s">
         <v>44</v>
       </c>
-      <c r="O2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>51</v>
-      </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
       <c r="T2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -1462,22 +1487,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>5</v>
@@ -1489,10 +1514,10 @@
         <v>5</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>5</v>
@@ -1516,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -1530,20 +1555,20 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
+      <c r="C4" t="s">
+        <v>110</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>300</v>
       </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
+      <c r="G4" t="s">
+        <v>26</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1554,11 +1579,11 @@
       <c r="J4">
         <v>-1</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4">
-        <v>-1</v>
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1581,8 +1606,8 @@
       <c r="S4">
         <v>-1</v>
       </c>
-      <c r="T4" t="s">
-        <v>114</v>
+      <c r="T4">
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -1590,22 +1615,22 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <v>500</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
+      <c r="G5" t="s">
+        <v>26</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1616,11 +1641,11 @@
       <c r="J5">
         <v>-1</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5">
-        <v>-1</v>
+      <c r="K5">
+        <v>-1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1643,8 +1668,8 @@
       <c r="S5">
         <v>-1</v>
       </c>
-      <c r="T5" t="s">
-        <v>112</v>
+      <c r="T5">
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -1652,22 +1677,22 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
         <v>800</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
+      <c r="G6" t="s">
+        <v>26</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1678,11 +1703,11 @@
       <c r="J6">
         <v>-1</v>
       </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6">
-        <v>-1</v>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1705,8 +1730,8 @@
       <c r="S6">
         <v>-1</v>
       </c>
-      <c r="T6" t="s">
-        <v>113</v>
+      <c r="T6">
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -1714,22 +1739,22 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>200</v>
       </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
+      <c r="G7" t="s">
+        <v>26</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1738,13 +1763,13 @@
         <v>-1</v>
       </c>
       <c r="J7">
+        <v>-1</v>
+      </c>
+      <c r="K7">
         <v>210015</v>
       </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
-        <v>-1</v>
+      <c r="L7" t="s">
+        <v>27</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1767,8 +1792,8 @@
       <c r="S7">
         <v>-1</v>
       </c>
-      <c r="T7" t="s">
-        <v>116</v>
+      <c r="T7">
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1776,22 +1801,22 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="C8" t="s">
+        <v>111</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>200</v>
       </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
+      <c r="G8" t="s">
+        <v>26</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1800,13 +1825,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
+        <v>-1</v>
+      </c>
+      <c r="K8">
         <v>210016</v>
       </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>-1</v>
+      <c r="L8" t="s">
+        <v>27</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1829,8 +1854,8 @@
       <c r="S8">
         <v>-1</v>
       </c>
-      <c r="T8" t="s">
-        <v>115</v>
+      <c r="T8">
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -1838,22 +1863,22 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>113</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <v>300</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
+      <c r="G9" t="s">
+        <v>26</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1862,13 +1887,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
+        <v>-1</v>
+      </c>
+      <c r="K9">
         <v>210017</v>
       </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9">
-        <v>-1</v>
+      <c r="L9" t="s">
+        <v>27</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1891,8 +1916,8 @@
       <c r="S9">
         <v>-1</v>
       </c>
-      <c r="T9" t="s">
-        <v>117</v>
+      <c r="T9">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1918,10 +1943,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1932,19 +1957,19 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1956,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -1973,13 +1998,13 @@
         <v>9999</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2015,15 +2040,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="D1" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2034,22 +2059,22 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2061,7 +2086,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>5</v>
@@ -2087,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -2107,13 +2132,13 @@
         <v>21002</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -2133,13 +2158,13 @@
         <v>21003</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -2159,13 +2184,13 @@
         <v>21004</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -2208,34 +2233,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" t="s">
         <v>67</v>
-      </c>
-      <c r="J2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2245,13 +2270,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -2260,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -2277,16 +2302,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -2295,7 +2320,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2309,19 +2334,19 @@
         <v>210012</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2330,10 +2355,10 @@
         <v>-1</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -2344,19 +2369,19 @@
         <v>210013</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -2365,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2379,19 +2404,19 @@
         <v>210014</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -2400,13 +2425,13 @@
         <v>-1</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2414,19 +2439,19 @@
         <v>210015</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2435,10 +2460,10 @@
         <v>-1</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -2449,19 +2474,19 @@
         <v>210016</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -2470,13 +2495,13 @@
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2484,19 +2509,19 @@
         <v>210017</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -2505,7 +2530,7 @@
         <v>-1</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624588DC-5C54-439F-AA0C-52B983F5AD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4161BA-B5F4-4845-811A-F2785E618101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="131">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -101,10 +101,6 @@
   </si>
   <si>
     <t>#desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pirze</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -537,6 +533,30 @@
   </si>
   <si>
     <t>Assets/m1_tmp/card_img/Mana_Potion.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string(128)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pow300이하 적 유닛 1장 파괴(승점X)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 덱에서 드로우 1장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드의 자신의 유닛 1체 pow+200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신의 마나 2 증가(이번턴)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prize</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -544,7 +564,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,8 +610,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,6 +679,11 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -705,12 +738,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -741,10 +777,11 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="3" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
+    <cellStyle name="강조색5" xfId="3" builtinId="45"/>
     <cellStyle name="보통" xfId="1" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -795,7 +832,7 @@
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
     <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#decs"/>
-    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="pirze"/>
+    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
     <tableColumn id="19" xr3:uid="{3E5C884A-7EF6-4486-A1A0-D6FED59BF178}" name="on_play_condition_type"/>
@@ -834,11 +871,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:H7" totalsRowShown="0" tableBorderDxfId="0">
-  <autoFilter ref="A2:H7" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:I7" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="A2:I7" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8D4780BB-DB0E-4DB7-98EE-B9656815F7E3}" name="id"/>
-    <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#desc"/>
+    <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#name"/>
+    <tableColumn id="9" xr3:uid="{F058E14E-AA4C-45AF-9E9C-7C8B9FA6C2D8}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{E1E06BC9-C21F-44D1-AEEB-BA85426B8332}" name="skill_cost"/>
     <tableColumn id="4" xr3:uid="{B1591891-D015-470D-84EF-F5BCE8D0B39A}" name="use_condition_type"/>
     <tableColumn id="5" xr3:uid="{679497A7-A7A1-4666-85D3-098B0B4B862D}" name="use_condition_value1"/>
@@ -1145,7 +1183,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1162,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1179,7 +1217,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1204,7 +1242,7 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -1213,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1221,7 +1259,7 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1230,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1238,7 +1276,7 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -1247,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1255,7 +1293,7 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -1264,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1272,7 +1310,7 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -1281,7 +1319,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1298,7 +1336,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1306,7 +1344,7 @@
         <v>21002</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>14</v>
@@ -1315,7 +1353,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1323,7 +1361,7 @@
         <v>21003</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -1332,7 +1370,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1340,7 +1378,7 @@
         <v>21004</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>14</v>
@@ -1348,8 +1386,8 @@
       <c r="D13" s="17">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>125</v>
+      <c r="E13" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1383,41 +1421,41 @@
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="S1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -1425,61 +1463,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
       <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>39</v>
       </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" t="s">
         <v>48</v>
       </c>
-      <c r="R2" t="s">
-        <v>49</v>
-      </c>
       <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" t="s">
         <v>44</v>
-      </c>
-      <c r="T2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -1487,10 +1525,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>12</v>
@@ -1502,7 +1540,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>5</v>
@@ -1517,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>5</v>
@@ -1556,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1568,22 +1606,22 @@
         <v>300</v>
       </c>
       <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
+        <v>-1</v>
+      </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4" t="s">
         <v>26</v>
-      </c>
-      <c r="H4">
-        <v>-1</v>
-      </c>
-      <c r="I4">
-        <v>-1</v>
-      </c>
-      <c r="J4">
-        <v>-1</v>
-      </c>
-      <c r="K4">
-        <v>-1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1615,10 +1653,10 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1630,22 +1668,22 @@
         <v>500</v>
       </c>
       <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>-1</v>
+      </c>
+      <c r="I5">
+        <v>-1</v>
+      </c>
+      <c r="J5">
+        <v>-1</v>
+      </c>
+      <c r="K5">
+        <v>-1</v>
+      </c>
+      <c r="L5" t="s">
         <v>26</v>
-      </c>
-      <c r="H5">
-        <v>-1</v>
-      </c>
-      <c r="I5">
-        <v>-1</v>
-      </c>
-      <c r="J5">
-        <v>-1</v>
-      </c>
-      <c r="K5">
-        <v>-1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1677,10 +1715,10 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1692,22 +1730,22 @@
         <v>800</v>
       </c>
       <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+      <c r="J6">
+        <v>-1</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6" t="s">
         <v>26</v>
-      </c>
-      <c r="H6">
-        <v>-1</v>
-      </c>
-      <c r="I6">
-        <v>-1</v>
-      </c>
-      <c r="J6">
-        <v>-1</v>
-      </c>
-      <c r="K6">
-        <v>-1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1739,10 +1777,10 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1754,7 +1792,7 @@
         <v>200</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1769,7 +1807,7 @@
         <v>210015</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1801,10 +1839,10 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1816,7 +1854,7 @@
         <v>200</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1831,7 +1869,7 @@
         <v>210016</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1863,10 +1901,10 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1878,7 +1916,7 @@
         <v>300</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1893,7 +1931,7 @@
         <v>210017</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1943,10 +1981,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1957,19 +1995,19 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1981,7 +2019,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -1998,13 +2036,13 @@
         <v>9999</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2027,69 +2065,75 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D387B383-5476-4EAA-BAC3-1341BA705F84}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="D1" s="5" t="s">
+    <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
         <v>61</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" t="s">
         <v>80</v>
       </c>
-      <c r="H2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
@@ -2100,22 +2144,25 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>21001</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>-1</v>
+      <c r="E4" t="s">
+        <v>25</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -2124,24 +2171,27 @@
         <v>-1</v>
       </c>
       <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
         <v>210011</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>21002</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5">
-        <v>-1</v>
+      <c r="E5" t="s">
+        <v>93</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -2150,24 +2200,27 @@
         <v>-1</v>
       </c>
       <c r="H5">
+        <v>-1</v>
+      </c>
+      <c r="I5">
         <v>210012</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>21003</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6">
-        <v>-1</v>
+      <c r="E6" t="s">
+        <v>92</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -2176,24 +2229,27 @@
         <v>-1</v>
       </c>
       <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6">
         <v>210013</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>21004</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
+      <c r="E7" t="s">
+        <v>90</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -2202,6 +2258,9 @@
         <v>-1</v>
       </c>
       <c r="H7">
+        <v>-1</v>
+      </c>
+      <c r="I7">
         <v>210014</v>
       </c>
     </row>
@@ -2233,34 +2292,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
         <v>72</v>
       </c>
-      <c r="E2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" t="s">
-        <v>73</v>
-      </c>
       <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
         <v>77</v>
       </c>
-      <c r="H2" t="s">
-        <v>78</v>
-      </c>
       <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
         <v>65</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>66</v>
-      </c>
-      <c r="K2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2270,13 +2329,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -2285,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -2302,16 +2361,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -2320,7 +2379,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2334,19 +2393,19 @@
         <v>210012</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2355,7 +2414,7 @@
         <v>-1</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2369,19 +2428,19 @@
         <v>210013</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -2390,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2404,28 +2463,28 @@
         <v>210014</v>
       </c>
       <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7">
+        <v>-1</v>
+      </c>
+      <c r="I7" t="s">
         <v>89</v>
-      </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-      <c r="H7">
-        <v>-1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>90</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2439,19 +2498,19 @@
         <v>210015</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2460,7 +2519,7 @@
         <v>-1</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2474,19 +2533,19 @@
         <v>210016</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -2495,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2509,19 +2568,19 @@
         <v>210017</v>
       </c>
       <c r="B10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" t="s">
         <v>106</v>
       </c>
-      <c r="C10" t="s">
-        <v>107</v>
-      </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -2530,7 +2589,7 @@
         <v>-1</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4161BA-B5F4-4845-811A-F2785E618101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220A08E-D28A-4A65-B8E6-4150823A1752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -371,10 +371,6 @@
   </si>
   <si>
     <t>String(64)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>#decs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -831,7 +827,7 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
-    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#decs"/>
+    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
@@ -1234,7 +1230,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1242,7 +1238,7 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -1251,7 +1247,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1259,7 +1255,7 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1268,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1276,7 +1272,7 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -1285,7 +1281,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1293,7 +1289,7 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -1302,7 +1298,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1310,7 +1306,7 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -1319,7 +1315,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1336,7 +1332,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1344,7 +1340,7 @@
         <v>21002</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>14</v>
@@ -1353,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1361,7 +1357,7 @@
         <v>21003</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -1370,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1378,7 +1374,7 @@
         <v>21004</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>14</v>
@@ -1387,7 +1383,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1421,7 +1417,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>28</v>
@@ -1463,13 +1459,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1594,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1653,10 +1649,10 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1715,10 +1711,10 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1777,10 +1773,10 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1839,10 +1835,10 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1901,10 +1897,10 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2095,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -2127,7 +2123,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>11</v>
@@ -2156,7 +2152,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -2182,16 +2178,16 @@
         <v>21002</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -2211,16 +2207,16 @@
         <v>21003</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -2240,16 +2236,16 @@
         <v>21004</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -2393,19 +2389,19 @@
         <v>210012</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2414,7 +2410,7 @@
         <v>-1</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2428,13 +2424,13 @@
         <v>210013</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2449,7 +2445,7 @@
         <v>-1</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2463,13 +2459,13 @@
         <v>210014</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -2484,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2498,19 +2494,19 @@
         <v>210015</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2519,7 +2515,7 @@
         <v>-1</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2533,10 +2529,10 @@
         <v>210016</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
         <v>69</v>
@@ -2554,7 +2550,7 @@
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2568,10 +2564,10 @@
         <v>210017</v>
       </c>
       <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
         <v>105</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220A08E-D28A-4A65-B8E6-4150823A1752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB29B5-6AF8-4268-B67D-9CB4C4B138F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28590" yWindow="-1905" windowWidth="16410" windowHeight="18315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -560,7 +560,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,8 +614,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,6 +685,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -746,7 +759,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -774,6 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
@@ -1226,8 +1240,8 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4">
-        <v>2</v>
+      <c r="D4" s="19">
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220A08E-D28A-4A65-B8E6-4150823A1752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105BF1D7-B423-40DC-A81F-28609C0FE022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="134">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -553,6 +553,22 @@
   </si>
   <si>
     <t>prize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 슬라임</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신은 이번턴 마나 1를 얻는다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장시 자신은 이번턴 마나 1을 획득한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/u_Gold_Slime.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -808,8 +824,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E13" totalsRowShown="0">
-  <autoFilter ref="A2:E13" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E14" totalsRowShown="0">
+  <autoFilter ref="A2:E14" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AA48A7AE-3BB5-4D28-B310-C246BE1D73A9}" name="id"/>
     <tableColumn id="2" xr3:uid="{736DFCAA-9BE9-4E13-AC78-9D961C82FC72}" name="name"/>
@@ -822,8 +838,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T9" totalsRowShown="0">
-  <autoFilter ref="A2:T9" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T10" totalsRowShown="0">
+  <autoFilter ref="A2:T10" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
@@ -885,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K10" totalsRowShown="0">
-  <autoFilter ref="A2:K10" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K11" totalsRowShown="0">
+  <autoFilter ref="A2:K11" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{293ED03F-3ECA-45BE-AFB4-C19E49058BDA}" name="id"/>
     <tableColumn id="2" xr3:uid="{301FB54A-AD16-4587-A00B-B96F748C89A7}" name="#group"/>
@@ -1167,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1320,69 +1336,86 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>21001</v>
+        <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>21001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
         <v>21002</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B12" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D12" s="14">
         <v>2</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>21003</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>86</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
         <v>21004</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D14" s="17">
         <v>2</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1397,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E6BAE-6D4F-4269-A5A9-7C25ADDEB0D7}">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -1951,6 +1984,68 @@
         <v>-1</v>
       </c>
       <c r="T9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>11007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+      <c r="J10">
+        <v>-1</v>
+      </c>
+      <c r="K10">
+        <v>210018</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10">
+        <v>-1</v>
+      </c>
+      <c r="N10">
+        <v>-1</v>
+      </c>
+      <c r="O10">
+        <v>-1</v>
+      </c>
+      <c r="P10">
+        <v>-1</v>
+      </c>
+      <c r="Q10">
+        <v>-1</v>
+      </c>
+      <c r="R10">
+        <v>-1</v>
+      </c>
+      <c r="S10">
+        <v>-1</v>
+      </c>
+      <c r="T10">
         <v>-1</v>
       </c>
     </row>
@@ -2271,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9DDD54-1F13-4B9B-9D90-4E3358700141}">
-  <dimension ref="A2:K10"/>
+  <dimension ref="A2:K11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -2594,6 +2689,41 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>210018</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11">
+        <v>-1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+      <c r="H11">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EB29B5-6AF8-4268-B67D-9CB4C4B138F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105BF1D7-B423-40DC-A81F-28609C0FE022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28590" yWindow="-1905" windowWidth="16410" windowHeight="18315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="134">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -553,6 +553,22 @@
   </si>
   <si>
     <t>prize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 슬라임</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신은 이번턴 마나 1를 얻는다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장시 자신은 이번턴 마나 1을 획득한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/m1_tmp/card_img/u_Gold_Slime.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +576,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,15 +630,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -685,12 +694,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -759,7 +762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -787,7 +790,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
@@ -822,8 +824,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E13" totalsRowShown="0">
-  <autoFilter ref="A2:E13" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E14" totalsRowShown="0">
+  <autoFilter ref="A2:E14" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AA48A7AE-3BB5-4D28-B310-C246BE1D73A9}" name="id"/>
     <tableColumn id="2" xr3:uid="{736DFCAA-9BE9-4E13-AC78-9D961C82FC72}" name="name"/>
@@ -836,8 +838,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T9" totalsRowShown="0">
-  <autoFilter ref="A2:T9" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:T10" totalsRowShown="0">
+  <autoFilter ref="A2:T10" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
@@ -899,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K10" totalsRowShown="0">
-  <autoFilter ref="A2:K10" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K11" totalsRowShown="0">
+  <autoFilter ref="A2:K11" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{293ED03F-3ECA-45BE-AFB4-C19E49058BDA}" name="id"/>
     <tableColumn id="2" xr3:uid="{301FB54A-AD16-4587-A00B-B96F748C89A7}" name="#group"/>
@@ -1181,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1240,8 +1242,8 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="19">
-        <v>20</v>
+      <c r="D4">
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -1334,69 +1336,86 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>21001</v>
+        <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>21001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
         <v>21002</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B12" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D12" s="14">
         <v>2</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>21003</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>86</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
         <v>21004</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D14" s="17">
         <v>2</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1411,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E6BAE-6D4F-4269-A5A9-7C25ADDEB0D7}">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -1965,6 +1984,68 @@
         <v>-1</v>
       </c>
       <c r="T9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>11007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+      <c r="J10">
+        <v>-1</v>
+      </c>
+      <c r="K10">
+        <v>210018</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10">
+        <v>-1</v>
+      </c>
+      <c r="N10">
+        <v>-1</v>
+      </c>
+      <c r="O10">
+        <v>-1</v>
+      </c>
+      <c r="P10">
+        <v>-1</v>
+      </c>
+      <c r="Q10">
+        <v>-1</v>
+      </c>
+      <c r="R10">
+        <v>-1</v>
+      </c>
+      <c r="S10">
+        <v>-1</v>
+      </c>
+      <c r="T10">
         <v>-1</v>
       </c>
     </row>
@@ -2285,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9DDD54-1F13-4B9B-9D90-4E3358700141}">
-  <dimension ref="A2:K10"/>
+  <dimension ref="A2:K11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -2608,6 +2689,41 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>210018</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11">
+        <v>-1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+      <c r="H11">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105BF1D7-B423-40DC-A81F-28609C0FE022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FAF91E-0565-42F3-A929-3A011383B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1243,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FAF91E-0565-42F3-A929-3A011383B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF3F761-7766-4A33-B4E7-94871351AC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF3F761-7766-4A33-B4E7-94871351AC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF1CD01-97C5-48C4-9527-55D91D7F9BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,46 +492,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/m1_tmp/card_img/u_slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Red_Slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/King_Slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Small_Worm.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Pixie_Dragon.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Bomb_Bee.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/s_fire_ball.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Learning.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Strengthen_Potion.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/m1_tmp/card_img/Mana_Potion.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>string(128)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -568,8 +528,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/m1_tmp/card_img/u_Gold_Slime.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Assets/Resources/card_img/u_slime.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Red_Slime.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/King_Slime.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Small_Worm.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Pixie_Dragon.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Bomb_Bee.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/u_Gold_Slime.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/s_fire_ball.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Learning.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Strengthen_Potion.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources/card_img/Mana_Potion.png</t>
   </si>
 </sst>
 </file>
@@ -631,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,12 +672,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
@@ -758,11 +741,11 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -782,14 +765,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - 강조색1" xfId="2" builtinId="30"/>
@@ -1183,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1193,12 +1177,12 @@
     <col min="6" max="7" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1232,192 +1216,211 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>11001</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="13">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="E4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>11002</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="E5" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>11003</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="E6" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>11004</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="13">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="E7" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>11005</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="13">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="E8" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>11006</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="13">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="E9" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>11007</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>21001</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10">
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>21002</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="16">
         <v>2</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>21003</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>21004</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="19">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>21001</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
-        <v>21002</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="14">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>21003</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
-        <v>21004</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="17">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>123</v>
-      </c>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1449,7 +1452,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -1498,7 +1501,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1992,10 +1995,10 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2217,8 +2220,8 @@
       <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>124</v>
+      <c r="C3" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>11</v>
@@ -2247,7 +2250,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -2276,7 +2279,7 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2305,7 +2308,7 @@
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2334,7 +2337,7 @@
         <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2694,10 +2697,10 @@
         <v>210018</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF1CD01-97C5-48C4-9527-55D91D7F9BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14C2658-AAF2-4C72-8251-DF020AC1487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -492,10 +492,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>string(128)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>pow300이하 적 유닛 1장 파괴(승점X)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -559,6 +555,10 @@
   </si>
   <si>
     <t>Assets/Resources/card_img/Mana_Potion.png</t>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -745,7 +745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -767,12 +767,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -827,7 +825,7 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
     <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#name"/>
-    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="#desc"/>
+    <tableColumn id="4" xr3:uid="{4265547F-DD0C-47BC-9461-16331FFAC9E4}" name="desc"/>
     <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="prize"/>
     <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
     <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
@@ -872,7 +870,7 @@
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8D4780BB-DB0E-4DB7-98EE-B9656815F7E3}" name="id"/>
     <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#name"/>
-    <tableColumn id="9" xr3:uid="{F058E14E-AA4C-45AF-9E9C-7C8B9FA6C2D8}" name="#desc"/>
+    <tableColumn id="9" xr3:uid="{F058E14E-AA4C-45AF-9E9C-7C8B9FA6C2D8}" name="desc"/>
     <tableColumn id="3" xr3:uid="{E1E06BC9-C21F-44D1-AEEB-BA85426B8332}" name="skill_cost"/>
     <tableColumn id="4" xr3:uid="{B1591891-D015-470D-84EF-F5BCE8D0B39A}" name="use_condition_type"/>
     <tableColumn id="5" xr3:uid="{679497A7-A7A1-4666-85D3-098B0B4B862D}" name="use_condition_value1"/>
@@ -1167,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1177,12 +1175,12 @@
     <col min="6" max="7" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1216,211 +1214,192 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>11001</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4">
         <v>20</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>11002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
-        <v>11002</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>11003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E6" t="s">
         <v>124</v>
       </c>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
-        <v>11003</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E7" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>11004</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E8" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
-        <v>11005</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="13" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>11006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E9" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>11006</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>11007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E10" t="s">
         <v>128</v>
       </c>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>11007</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="13">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>21001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
         <v>2</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E11" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>21001</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="13" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>21002</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D12" s="14">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E12" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
-        <v>21002</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="15" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>21003</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D13">
         <v>2</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E13" t="s">
         <v>131</v>
       </c>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>21003</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
+        <v>21004</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D14" s="17">
         <v>2</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E14" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <v>21004</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="19">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1498,10 +1477,10 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1995,10 +1974,10 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2192,7 +2171,7 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>56</v>
@@ -2221,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>11</v>
@@ -2250,7 +2229,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -2279,7 +2258,7 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2308,7 +2287,7 @@
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2337,7 +2316,7 @@
         <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2697,10 +2676,10 @@
         <v>210018</v>
       </c>
       <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s">
         <v>120</v>
-      </c>
-      <c r="C11" t="s">
-        <v>121</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14C2658-AAF2-4C72-8251-DF020AC1487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051CE217-CBC0-4C46-9E1C-56324EA9A78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -433,9 +433,6 @@
     <t>OwnMana</t>
   </si>
   <si>
-    <t>DeckHighOrEqual</t>
-  </si>
-  <si>
     <t>레드슬라임</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -484,10 +481,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DamegeToUnit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>적 1장 데미지 200(승점X)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -520,10 +513,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>등장시 자신은 이번턴 마나 1을 획득한다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Resources/card_img/u_slime.png</t>
   </si>
   <si>
@@ -558,6 +547,18 @@
   </si>
   <si>
     <t>desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageToUnit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeckMoreOrEqual</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장 시 자신은 이번턴 마나 1을 획득한다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1228,7 +1229,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1236,7 +1237,7 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -1245,7 +1246,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,7 +1254,7 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1262,7 +1263,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,7 +1271,7 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -1279,7 +1280,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1287,7 +1288,7 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -1296,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1304,7 +1305,7 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -1313,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,7 +1322,7 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -1330,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1347,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1364,7 +1365,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1381,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1398,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1477,10 +1478,10 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1605,7 +1606,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1664,10 +1665,10 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1726,10 +1727,10 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1788,10 +1789,10 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1850,10 +1851,10 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1912,10 +1913,10 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1974,10 +1975,10 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2171,7 +2172,7 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>56</v>
@@ -2229,7 +2230,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -2258,7 +2259,7 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2287,7 +2288,7 @@
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2316,7 +2317,7 @@
         <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2478,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2571,7 +2572,7 @@
         <v>210015</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
         <v>93</v>
@@ -2583,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2606,10 +2607,10 @@
         <v>210016</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
         <v>69</v>
@@ -2627,7 +2628,7 @@
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2641,10 +2642,10 @@
         <v>210017</v>
       </c>
       <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
         <v>104</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
@@ -2676,10 +2677,10 @@
         <v>210018</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>

--- a/GameDesign/Storage/SampleData/Card.xlsx
+++ b/GameDesign/Storage/SampleData/Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051CE217-CBC0-4C46-9E1C-56324EA9A78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA4391D-0F5C-4AE4-A7D4-C32ED698ECB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="135">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -269,10 +269,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>스칼 카드 사용 조건</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 카드 사용 직전 효과
 (ex 릴리스 소재)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -397,17 +393,9 @@
     <t>Gain_Mana</t>
   </si>
   <si>
-    <t>Gain_Mana</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Power_Up</t>
   </si>
   <si>
-    <t>Power_Up</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Draw</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -559,6 +547,22 @@
   </si>
   <si>
     <t>등장 시 자신은 이번턴 마나 1을 획득한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 카드 사용 조건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyUnitExist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnUnitExist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardCondition</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1229,7 +1233,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1237,7 +1241,7 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -1246,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1254,7 +1258,7 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -1263,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1271,7 +1275,7 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -1280,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1288,7 +1292,7 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -1297,7 +1301,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1305,7 +1309,7 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -1314,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1322,7 +1326,7 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -1331,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1348,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1356,7 +1360,7 @@
         <v>21002</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
@@ -1365,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1373,7 +1377,7 @@
         <v>21003</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -1382,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1390,7 +1394,7 @@
         <v>21004</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>14</v>
@@ -1399,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1437,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>28</v>
@@ -1475,13 +1479,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1517,7 +1521,7 @@
         <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="s">
         <v>47</v>
@@ -1537,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
@@ -1606,7 +1610,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1665,10 +1669,10 @@
         <v>11002</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1727,10 +1731,10 @@
         <v>11003</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1789,10 +1793,10 @@
         <v>11004</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1851,10 +1855,10 @@
         <v>11005</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1913,10 +1917,10 @@
         <v>11006</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1975,10 +1979,10 @@
         <v>11007</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2153,15 +2157,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="E1" s="5" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2169,28 +2173,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
       <c r="H2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" t="s">
         <v>79</v>
-      </c>
-      <c r="I2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2207,7 +2211,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
@@ -2230,16 +2234,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -2256,16 +2260,16 @@
         <v>21002</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -2285,19 +2289,19 @@
         <v>21003</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -2314,16 +2318,16 @@
         <v>21004</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -2366,34 +2370,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" t="s">
         <v>71</v>
       </c>
-      <c r="E2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
       <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
         <v>76</v>
       </c>
-      <c r="H2" t="s">
-        <v>77</v>
-      </c>
       <c r="I2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" t="s">
         <v>64</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2403,13 +2407,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>6</v>
@@ -2418,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>6</v>
@@ -2435,16 +2439,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -2453,7 +2457,7 @@
         <v>-1</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2467,19 +2471,19 @@
         <v>210012</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
         <v>93</v>
       </c>
-      <c r="D5" t="s">
-        <v>96</v>
-      </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2488,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2502,13 +2506,13 @@
         <v>210013</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
         <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2523,7 +2527,7 @@
         <v>-1</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2537,13 +2541,13 @@
         <v>210014</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
         <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -2558,7 +2562,7 @@
         <v>-1</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2572,19 +2576,19 @@
         <v>210015</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
         <v>93</v>
       </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2593,7 +2597,7 @@
         <v>-1</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2607,13 +2611,13 @@
         <v>210016</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2628,7 +2632,7 @@
         <v>-1</v>
       </c>
       <c r="I9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2642,13 +2646,13 @@
         <v>210017</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2663,7 +2667,7 @@
         <v>-1</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2677,13 +2681,13 @@
         <v>210018</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -2698,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11">
         <v>0</v>
